--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20910"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14180" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20580" windowHeight="11640" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$51</definedName>
   </definedNames>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="124519" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -221,14 +221,26 @@
   </si>
   <si>
     <t>图形化部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,10 +311,78 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="普通" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -314,7 +394,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -627,12 +707,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -774,206 +854,227 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
-        <v>46</v>
+      <c r="A33" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>47</v>
+      <c r="A34" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>48</v>
+      <c r="A35" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>49</v>
+      <c r="A36" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
-        <v>31</v>
+      <c r="A37" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>34</v>
+      <c r="A40" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
-        <v>37</v>
+      <c r="A43" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>39</v>
+      <c r="A46" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
-        <v>41</v>
+      <c r="A47" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$52</definedName>
   </definedNames>
   <calcPr calcId="124519" concurrentCalc="0"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,171 +68,175 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户鉴权</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宕机重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉电重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多份复制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单份复制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据损坏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>均匀性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同操作并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合操作并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C/C++</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Python</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadoop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易用性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和对标产品对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令行安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图形化安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令行部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图形化部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>垂直切分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安全性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户鉴权</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可靠性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宕机重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉电重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多份复制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单份复制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据损坏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>均匀性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据分布</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>性能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小于内存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大于内存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同操作并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>混合操作并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C/C++</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Python</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三方</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hadoop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PostgreSQL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>易用性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>和对标产品对比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否相关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装部署</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令行安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图形化安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令行部署</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图形化部署</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网</t>
+    <t>事务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -708,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -720,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -798,70 +802,70 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -875,206 +879,213 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
+      <c r="A26" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>23</v>
+      <c r="A27" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>24</v>
+      <c r="A28" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>25</v>
+      <c r="A29" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>26</v>
+      <c r="A30" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>27</v>
+      <c r="A31" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
-        <v>28</v>
+      <c r="A32" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>29</v>
+      <c r="A33" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
-        <v>45</v>
+      <c r="A35" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="3" t="s">
-        <v>46</v>
+      <c r="A36" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
-        <v>48</v>
+      <c r="A38" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
-        <v>31</v>
+      <c r="A40" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>32</v>
+      <c r="A41" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
-        <v>37</v>
+      <c r="A46" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>40</v>
+      <c r="A47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
-        <v>41</v>
+      <c r="A50" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>42</v>
+      <c r="A51" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20580" windowHeight="11640" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="8265" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="数据同步" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$52</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -237,6 +238,162 @@
   </si>
   <si>
     <t>事务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据存储</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引存储</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔离性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多份复制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据损坏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>均匀性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同操作并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令行安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图形化安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令行部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图形化部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C/C++</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadoop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务回滚和commit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步时，生成索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与源节点同步数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初步相关性分析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前测试覆盖模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终分析结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步时，保存数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +401,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -260,8 +417,47 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,6 +473,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -308,11 +510,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,4 +1308,604 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.875" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -241,6 +241,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>是否相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>数据存储</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -361,39 +365,121 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>元数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务回滚和commit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同步时，生成索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与源节点同步数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初步相关性分析</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前测试覆盖模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最终分析结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步时，保存数据</t>
+    <t>？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>考虑1.2G临界点、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>日志文件大小、个数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟mongo同步的性能对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在两个唯一键index的情况下，update可以修改oid。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>测试需要考虑oid修改的场景</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注备节点能否正常回放？主备数据是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注备节点能否正常回放？索引是否在备节点能否正常生成索引？主备数据是否一致？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注大数据块，临界数据块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改操作能够同步到备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步本身涉及日志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点从备份中恢复后， 其他能否同步到数据。考虑节点异常情况下能否正常同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储过程存储在catalog上，备catalog能否正常同步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备catalog同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务回滚和commit能否正常同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑目的节点重复重启;同步过程中源节点切换;考虑多种异常组合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本地rebuild时异常;再次宕机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑掉电之后节点能否全部正常运行;所有节点掉电数据恢复情况，丢多少数据？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步应该正常且数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步应该正常且数据一致，主节点异常时会切主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测数据能否正常？ 恢复后数据是否可读写和是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点异常时，多份复制可以保证数据不丢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点异常时，数据可能丢失，但数据丢失量不大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑操作顺序是否一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1312,596 +1398,516 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.875" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="11" style="5"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5">
+        <v>84</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="C25" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5">
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5">
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5">
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5">
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5">
+        <v>83</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5">
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5">
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5">
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:5">
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5">
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:5">
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="1:5">
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" spans="1:5">
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="1:5">
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="1:5">
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="1:5">
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="1:5">
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-    </row>
-    <row r="49" spans="1:5">
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-    </row>
-    <row r="50" spans="1:5">
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" spans="1:5">
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:5">
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -411,75 +411,75 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>关注备节点能否正常回放？索引是否在备节点能否正常生成索引？主备数据是否一致？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注大数据块，临界数据块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改操作能够同步到备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同步本身涉及日志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点从备份中恢复后， 其他能否同步到数据。考虑节点异常情况下能否正常同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储过程存储在catalog上，备catalog能否正常同步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备catalog同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务回滚和commit能否正常同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑目的节点重复重启;同步过程中源节点切换;考虑多种异常组合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本地rebuild时异常;再次宕机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑掉电之后节点能否全部正常运行;所有节点掉电数据恢复情况，丢多少数据？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步应该正常且数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步应该正常且数据一致，主节点异常时会切主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测数据能否正常？ 恢复后数据是否可读写和是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点异常时，多份复制可以保证数据不丢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点异常时，数据可能丢失，但数据丢失量不大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑操作顺序是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>关注备节点能否正常回放？主备数据是否一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关注备节点能否正常回放？索引是否在备节点能否正常生成索引？主备数据是否一致？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关注大数据块，临界数据块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改操作能够同步到备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同步本身涉及日志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点从备份中恢复后， 其他能否同步到数据。考虑节点异常情况下能否正常同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存储过程存储在catalog上，备catalog能否正常同步。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备catalog同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务回滚和commit能否正常同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑目的节点重复重启;同步过程中源节点切换;考虑多种异常组合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本地rebuild时异常;再次宕机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑掉电之后节点能否全部正常运行;所有节点掉电数据恢复情况，丢多少数据？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据同步应该正常且数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据同步应该正常且数据一致，主节点异常时会切主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>观测数据能否正常？ 恢复后数据是否可读写和是否一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点异常时，多份复制可以保证数据不丢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点异常时，数据可能丢失，但数据丢失量不大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑操作顺序是否一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1433,7 +1433,7 @@
         <v>83</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1444,7 +1444,7 @@
         <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1455,7 +1455,7 @@
         <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1466,7 +1466,7 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1488,7 +1488,7 @@
         <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1499,7 +1499,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1510,7 +1510,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1521,7 +1521,7 @@
         <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1532,7 +1532,7 @@
         <v>83</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1543,7 +1543,7 @@
         <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1561,7 +1561,7 @@
         <v>83</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1572,7 +1572,7 @@
         <v>83</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1590,7 +1590,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1601,7 +1601,7 @@
         <v>83</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1612,7 +1612,7 @@
         <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1623,7 +1623,7 @@
         <v>83</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1634,7 +1634,7 @@
         <v>83</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1645,7 +1645,7 @@
         <v>83</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1656,7 +1656,7 @@
         <v>83</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1667,7 +1667,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>83</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:3">

--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -4,11 +4,21 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="8265" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="8265" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="数据同步" sheetId="2" r:id="rId2"/>
+    <sheet name="元数据操作" sheetId="4" r:id="rId3"/>
+    <sheet name="基本操作" sheetId="5" r:id="rId4"/>
+    <sheet name="split切分" sheetId="7" r:id="rId5"/>
+    <sheet name="主子表" sheetId="8" r:id="rId6"/>
+    <sheet name="集群管理" sheetId="3" r:id="rId7"/>
+    <sheet name="聚集" sheetId="12" r:id="rId8"/>
+    <sheet name="权限管理" sheetId="9" r:id="rId9"/>
+    <sheet name="rest" sheetId="6" r:id="rId10"/>
+    <sheet name="java驱动" sheetId="10" r:id="rId11"/>
+    <sheet name="c&amp;c++" sheetId="11" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$52</definedName>
@@ -23,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="163">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -459,10 +469,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据同步应该正常且数据一致，主节点异常时会切主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>观测数据能否正常？ 恢复后数据是否可读写和是否一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -480,6 +486,256 @@
   </si>
   <si>
     <t>关注备节点能否正常回放？主备数据是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog之间进行元数据同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注能否正常备份并恢复catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog元数据修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储过程内容存放在catalog中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog是否能正确鉴权</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启后元数据是否丢失；catalog多点重启后，数据恢复能否保证数据完整性和一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog重建时能否正常恢复？ 重建时又发生故障？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据是否保持一致;业务是否能否正常执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉电后节点能否恢复正常提供业务？重建后能否保证数据完整性？数据是否丢失？丢失程度？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据存储</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据表涉及索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">catalog切主后能否继续执行？ 断网恢复后能否恢复一致? </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog的replsize为&gt;=n/2 + 1, 多节点（少于多数派）同时故障数据应该保持一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时创建相同的cs、cl、节点组？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并行反复创建/删除表，同时在操作数据。确保数据完整性，如表不存在，数据节点不应该有数据；表存在时删除所属数据组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装失败回滚后元数据是否清空？ 安装过程中节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crud/index/lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性能、接口适配</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备份过程中进行基本数据操作？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作能否正确落到指定数据组中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作能否正确落到指定数据组中， 多个条件组合场景，能否正确执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作须正常回滚、commit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crud过程中，主备节点正常重启，关注数据是否一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多点宕机；数据恢复过程中进行大量数据操作，关注后续操作能否正常同步到备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多种重启组合；恢复过程中再次掉电；考虑一组一节点的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作应正常执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步应该正常且数据一致，断网切主后，原主多余的记录应该回退并更新到与新主一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作是否会一直挂起；恢复后能否正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点异常导致replsize不满足时，如何处理？ 恢复后数据是否一致？存活节点数大于等于replsize时，数据不应丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性能与之前版本是否有差异</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发lob操作/crud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对主备节点做不同考虑；断网切主后，旧主多余的记录应该回退并更新到与新主一致， 旧主积压的网络消息应该不被处理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分键冲突</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能接入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据存储分布在多个切分的数据组上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引存储分布在多个切分的数据组上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob与curd是否有冲突？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注lob数据是否均匀， 考虑lob数据与cl表的数据分布的不一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据切分之后，是否影响lob的分布（lob的切分以oid+sequence来切）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注切分键能否修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分时并发读写， 垂直切分+水平切分组合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分过程中宕机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分过程中多节点掉电，恢复后数据能否继续切分，并保证数据与切分前一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分布是否正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定条件的命令不会下发到分区键不相关的数据组中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能否正常落到正确的子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分是否正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach过程中catalog重启；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发attach子表，条件冲突</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach/attach过程中异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>保证数据与切分前一致，切分后读写可以参考基本操作，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>主要关注每个数据组中数据的完整性和独立性</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>参照基本操作的异常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，关注子表间的独立性和数据完整性是否被破坏</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发attach+数据操作；考虑水平+垂直并存的切分；单独对子表的操作是否影响主表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分过程中重启源节点/目的节点，切分任务是否能够恢复；异常恢复后能否读写数据、删除表等操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,7 +825,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -592,11 +848,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -610,6 +903,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1396,7 +1710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
@@ -1429,122 +1743,78 @@
       <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>107</v>
-      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>93</v>
-      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
@@ -1557,23 +1827,15 @@
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
@@ -1586,100 +1848,64 @@
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>100</v>
-      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>102</v>
-      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
@@ -1692,9 +1918,7 @@
       <c r="A28" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
@@ -1708,29 +1932,21 @@
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>83</v>
-      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:3">
@@ -1744,11 +1960,514 @@
       <c r="A34" s="4" t="s">
         <v>72</v>
       </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="B34" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1914,4 +2633,2817 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="24">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="24">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="24">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" ht="24">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="19"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C21:C23"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="15"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="15"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C20:C23"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/test_checklist.xlsx
+++ b/internal_doc/05.测试设计/test_checklist.xlsx
@@ -4,21 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="8265" tabRatio="500" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="8265" tabRatio="500" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="数据同步" sheetId="2" r:id="rId2"/>
+    <sheet name="数据全量同步" sheetId="2" r:id="rId2"/>
     <sheet name="元数据操作" sheetId="4" r:id="rId3"/>
     <sheet name="基本操作" sheetId="5" r:id="rId4"/>
     <sheet name="split切分" sheetId="7" r:id="rId5"/>
     <sheet name="主子表" sheetId="8" r:id="rId6"/>
     <sheet name="集群管理" sheetId="3" r:id="rId7"/>
     <sheet name="聚集" sheetId="12" r:id="rId8"/>
-    <sheet name="权限管理" sheetId="9" r:id="rId9"/>
-    <sheet name="rest" sheetId="6" r:id="rId10"/>
-    <sheet name="java驱动" sheetId="10" r:id="rId11"/>
-    <sheet name="c&amp;c++" sheetId="11" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$55</definedName>
@@ -33,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="201">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -876,6 +873,22 @@
   <si>
     <t>参数基本操作的异常用例
 coord节点网络异常恢复后，关注聚集操作能否正常终止。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据同步过程中异常场景展开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x轴细化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y轴细化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1889,1170 +1902,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
-  <cols>
-    <col min="1" max="1" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="11" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D55"/>
@@ -3242,7 +2091,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="8" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -6695,389 +5544,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12"/>
-  <cols>
-    <col min="1" max="1" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="11" style="2"/>
-  </cols>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
